--- a/Document/TestCases/TestCases-DemoWebShop.xlsx
+++ b/Document/TestCases/TestCases-DemoWebShop.xlsx
@@ -1,11 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30126"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8EF44E8-DC48-4CDB-BB8D-896A23E595E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9963c16bba70e78d/Documents/GitHub/AutomationWebShopDemo/Document/TestCases/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -15,10 +19,7 @@
     <sheet name="Cart" sheetId="5" r:id="rId5"/>
     <sheet name="Checkout" sheetId="6" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="124">
   <si>
     <t>Project Info</t>
   </si>
@@ -375,12 +376,51 @@
   </si>
   <si>
     <t>Bug-Wish-2</t>
+  </si>
+  <si>
+    <t>TC-Cart-04</t>
+  </si>
+  <si>
+    <t>TC-Cart-05</t>
+  </si>
+  <si>
+    <t>add any Product to cart</t>
+  </si>
+  <si>
+    <t>Open site go to the prduct was in home page choose the any product adding to cart and remove from cart</t>
+  </si>
+  <si>
+    <t>Product Should Be removed and deleted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open site go to the prduct was in home page choose the any product adding to cart </t>
+  </si>
+  <si>
+    <t>product prive was verify</t>
+  </si>
+  <si>
+    <t>TC-WISH-04</t>
+  </si>
+  <si>
+    <t>Remove Product From Wishlist</t>
+  </si>
+  <si>
+    <t>Product was Deleted.</t>
+  </si>
+  <si>
+    <t>Open Web Then select product then add to wishlist verify product can found in wishlist then Delete product</t>
+  </si>
+  <si>
+    <t>Remove Product From Cart</t>
+  </si>
+  <si>
+    <t>Verify Product Price In Cart</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="12">
     <font>
       <sz val="11"/>
@@ -401,7 +441,7 @@
       <b/>
       <sz val="12"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -409,7 +449,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -417,27 +457,27 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -482,7 +522,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -570,12 +610,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -602,6 +657,39 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -614,9 +702,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -626,44 +711,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -681,34 +739,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Login (DD)"/>
-      <sheetName val="Register (DD)"/>
-      <sheetName val="Home &amp; Navigation"/>
-      <sheetName val="Search &amp; Filter"/>
-      <sheetName val="Product Detail"/>
-      <sheetName val="Checkout"/>
-      <sheetName val="My Account"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1027,13 +1057,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="2.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" customWidth="1"/>
+    <col min="1" max="1" width="2.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.375" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1048,56 +1078,56 @@
       <c r="D1" s="18"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="14"/>
+      <c r="D2" s="19"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="19" t="s">
+      <c r="B3" s="19"/>
+      <c r="C3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="19"/>
+      <c r="D3" s="20"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="15">
+      <c r="B4" s="19"/>
+      <c r="C4" s="25">
         <v>46178</v>
       </c>
-      <c r="D4" s="15"/>
+      <c r="D4" s="25"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="16" t="s">
+      <c r="B5" s="27"/>
+      <c r="C5" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="17"/>
+      <c r="D5" s="27"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="27"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
     </row>
     <row r="8" spans="1:4" ht="15.75">
       <c r="A8" s="1" t="s">
@@ -1113,7 +1143,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" ht="15">
       <c r="A9" s="3">
         <v>1</v>
       </c>
@@ -1127,7 +1157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" ht="15">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -1141,7 +1171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" ht="15">
       <c r="A11" s="3">
         <v>3</v>
       </c>
@@ -1155,7 +1185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" ht="15">
       <c r="A12" s="3">
         <v>4</v>
       </c>
@@ -1166,7 +1196,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="29.25" customHeight="1">
@@ -1180,28 +1210,22 @@
         <v>21</v>
       </c>
       <c r="D13" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="24"/>
       <c r="D14" s="1">
         <f>SUM(D9:D13)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A4:B4"/>
@@ -1210,155 +1234,161 @@
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C3:D3" r:id="rId1" display="https://demowebshop.tricentis.com/" xr:uid="{9D343CD5-728C-45C2-A45A-9B6C3B731E40}"/>
+    <hyperlink ref="C3:D3" r:id="rId1" display="https://demowebshop.tricentis.com/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9C4F3C2-924E-41D3-8B7C-504974D6B9CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="18.625" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
+    <col min="4" max="4" width="22.75" customWidth="1"/>
+    <col min="5" max="5" width="18.625" customWidth="1"/>
+    <col min="6" max="6" width="16.75" customWidth="1"/>
+    <col min="7" max="7" width="17.125" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" customWidth="1"/>
+    <col min="9" max="9" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="36">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="57.75">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:10" ht="57">
+      <c r="A2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="10" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="57.75">
-      <c r="A3" s="21" t="s">
+    <row r="3" spans="1:10" ht="57">
+      <c r="A3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="10" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="57.75">
-      <c r="A4" s="21" t="s">
+    <row r="4" spans="1:10" ht="57">
+      <c r="A4" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="10" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1368,23 +1398,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{946CD9F6-5EB2-45D0-BB3F-786B0D3537B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="30.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="2" width="30.625" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
-    <col min="4" max="4" width="25.85546875" customWidth="1"/>
-    <col min="5" max="5" width="24.85546875" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
-    <col min="7" max="7" width="27.140625" customWidth="1"/>
-    <col min="8" max="8" width="21.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.875" customWidth="1"/>
+    <col min="5" max="5" width="24.875" customWidth="1"/>
+    <col min="6" max="6" width="17.125" customWidth="1"/>
+    <col min="7" max="7" width="27.125" customWidth="1"/>
+    <col min="8" max="8" width="21.75" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="36">
+    <row r="1" spans="1:10">
       <c r="A1" s="8" t="s">
         <v>23</v>
       </c>
@@ -1417,162 +1447,162 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="10" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="10" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="40.5" customHeight="1">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="10" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="10" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="39" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="10" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1582,20 +1612,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D01C373C-C7C8-424F-BBAD-340D5F1298A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" customWidth="1"/>
-    <col min="6" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" customWidth="1"/>
-    <col min="9" max="9" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15.75" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="15.375" customWidth="1"/>
+    <col min="5" max="5" width="13.125" customWidth="1"/>
+    <col min="6" max="7" width="14.125" customWidth="1"/>
+    <col min="8" max="8" width="10.375" customWidth="1"/>
+    <col min="9" max="9" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="36">
+    <row r="1" spans="1:10" ht="25.5">
       <c r="A1" s="8" t="s">
         <v>23</v>
       </c>
@@ -1620,7 +1650,7 @@
       <c r="H1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="11" t="s">
         <v>31</v>
       </c>
       <c r="J1" s="8" t="s">
@@ -1628,66 +1658,66 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="91.5" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="10" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="101.25">
-      <c r="A3" s="21" t="s">
+    <row r="3" spans="1:10" ht="85.5">
+      <c r="A3" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="10" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1697,21 +1727,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84AAFA3E-9B1B-4F09-B316-DAE9158B40A4}">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.75" customWidth="1"/>
+    <col min="3" max="3" width="14.625" customWidth="1"/>
+    <col min="4" max="4" width="16.75" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" customWidth="1"/>
-    <col min="9" max="9" width="21.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.75" customWidth="1"/>
+    <col min="7" max="7" width="19.625" customWidth="1"/>
+    <col min="8" max="8" width="16.875" customWidth="1"/>
+    <col min="9" max="9" width="21.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="36">
+    <row r="1" spans="1:10" ht="25.5">
       <c r="A1" s="8" t="s">
         <v>23</v>
       </c>
@@ -1743,99 +1773,163 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="57.75">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:10" ht="57">
+      <c r="A2" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="10" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="57.75">
-      <c r="A3" s="21" t="s">
+    <row r="3" spans="1:10" ht="57">
+      <c r="A3" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="10" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="72.75">
-      <c r="A4" s="21" t="s">
+    <row r="4" spans="1:10" ht="71.25">
+      <c r="A4" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="85.5">
+      <c r="A5" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="71.25">
+      <c r="A6" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1845,146 +1939,179 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E2ADBEC-80CE-4A6F-802F-EE40681BCBEC}">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.875" customWidth="1"/>
+    <col min="5" max="5" width="11.625" customWidth="1"/>
+    <col min="9" max="9" width="19.375" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="36">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:10" ht="25.5">
+      <c r="A1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="28" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72.75">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:10" ht="71.25">
+      <c r="A2" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="31" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="72.75">
-      <c r="A3" s="22" t="s">
+    <row r="3" spans="1:10" ht="71.25">
+      <c r="A3" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="31" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="108.75" customHeight="1">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="22"/>
-      <c r="E4" s="21" t="s">
+      <c r="D4" s="30"/>
+      <c r="E4" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="22" t="s">
+      <c r="J4" s="30" t="s">
         <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="142.5">
+      <c r="A5" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="31" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>